--- a/output/pdf_financials_xlsx/OVL.H.xlsx
+++ b/output/pdf_financials_xlsx/OVL.H.xlsx
@@ -4144,37 +4144,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.71036</v>
       </c>
     </row>
     <row r="93">
@@ -6773,7 +6773,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>1.71036</v>
       </c>

--- a/output/pdf_financials_xlsx/OVL.H.xlsx
+++ b/output/pdf_financials_xlsx/OVL.H.xlsx
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.264744</v>
+        <v>0.403366</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.226851</v>
+        <v>0.300704</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.224757</v>
+        <v>0.300831</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.098381</v>
+        <v>0.117472</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.050421</v>
+        <v>0.06855799999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.048972</v>
+        <v>0.057446</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.040125</v>
+        <v>0.050073</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.037976</v>
+        <v>0.048056</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.053135</v>
+        <v>0.081943</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.038431</v>
+        <v>0.052332</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.047592</v>
+        <v>0.080943</v>
       </c>
     </row>
     <row r="11">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.285498</v>
+        <v>-0.42412</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.260335</v>
+        <v>-0.334188</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.262076</v>
+        <v>-0.33815</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.133437</v>
+        <v>-0.152528</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.074999</v>
+        <v>-0.093136</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.096871</v>
+        <v>-0.105345</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.037976</v>
+        <v>-0.048056</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.053135</v>
+        <v>-0.081943</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.038431</v>
+        <v>-0.052332</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.047592</v>
+        <v>-0.080943</v>
       </c>
     </row>
     <row r="12">
@@ -1790,37 +1790,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001921</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000111</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.1e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000473</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000289</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000547</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000468</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000379</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.00028</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.06786499999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1870,37 +1870,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001921</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000111</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.1e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000473</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000289</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000547</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000468</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000379</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.00028</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.06786499999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2350,37 +2350,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.001921</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002386</v>
+        <v>0.002275</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.003035</v>
+        <v>0.002974</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.000473</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.000154</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000289</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.001422</v>
+        <v>0.000875</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.000468</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.000379</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.00028</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.072865</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="49">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">

--- a/output/pdf_financials_xlsx/OVL.H.xlsx
+++ b/output/pdf_financials_xlsx/OVL.H.xlsx
@@ -3012,37 +3012,37 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.061314</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.065571</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.189311</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.25687</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.312277</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.371484</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.375381</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.385162</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.4212</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.419423</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.789699</v>
       </c>
     </row>
     <row r="65">
@@ -4471,37 +4471,37 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.047472</v>
+        <v>-0.045346</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.046619</v>
+        <v>0.039917</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.000597</v>
+        <v>0.007443</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.002214</v>
+        <v>0.000635</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.009396</v>
+        <v>-0.011802</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.010192</v>
+        <v>0.011208</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.000622</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001743</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002612</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.003528</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002049</v>
       </c>
     </row>
     <row r="102">
@@ -4671,37 +4671,37 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.033335</v>
+        <v>-0.031209</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.112101</v>
+        <v>0.105399</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.187639</v>
+        <v>0.194485</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.13535</v>
+        <v>0.138199</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.113374</v>
+        <v>0.110968</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.133505</v>
+        <v>0.134521</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.069022</v>
+        <v>0.069644</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.077656</v>
+        <v>0.07591299999999999</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.106535</v>
+        <v>0.103923</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.060726</v>
+        <v>0.06425400000000001</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.454627</v>
+        <v>0.452578</v>
       </c>
     </row>
     <row r="107">
@@ -7976,7 +7976,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.002126</v>
       </c>
